--- a/InputData/hydgn/RHPF/Recipient Hydrogen Pathway Fractions.xlsx
+++ b/InputData/hydgn/RHPF/Recipient Hydrogen Pathway Fractions.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox (Energy Innovation)\EI-PlcyMdl\eps-1.5.0-us-wipD\InputData\hydgn\RHPF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndonesiaEPS/Shared Documents/Updated Indonesia InputData files/hydgn/RHPF/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_6505181553A7B84413D4CA40DDB3621ED7304027" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CD46B5E-B5CD-46C7-A0A9-50F6A19DC572}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25815" windowHeight="11970"/>
+    <workbookView xWindow="43095" yWindow="1080" windowWidth="14610" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
   <si>
     <t>RHPF Recipient Hydrogen Pathway Fractions</t>
   </si>
@@ -69,19 +70,25 @@
     <t>biomass gasification</t>
   </si>
   <si>
-    <t>thermochemical water splitting</t>
-  </si>
-  <si>
     <t>To type (below)  / From type (right)</t>
   </si>
   <si>
     <t>Ensure that every column adds to 1.</t>
   </si>
+  <si>
+    <t>hydrocarbon partial oxidation</t>
+  </si>
+  <si>
+    <t>electrolysis with guaranteed clean electricity</t>
+  </si>
+  <si>
+    <t>natural gas reforming with CCS</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -122,7 +129,6 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -130,6 +136,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -411,16 +420,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -428,44 +437,44 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -475,138 +484,421 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.28515625" customWidth="1"/>
-    <col min="2" max="6" width="16.5703125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="34.26953125" customWidth="1"/>
+    <col min="2" max="6" width="16.54296875" style="3" customWidth="1"/>
+    <col min="7" max="8" width="16.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4">
-        <v>1</v>
-      </c>
-      <c r="D2" s="4">
-        <v>1</v>
-      </c>
-      <c r="E2" s="4">
-        <v>1</v>
-      </c>
-      <c r="F2" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="3">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4">
-        <v>0</v>
-      </c>
-      <c r="C3" s="4">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="3">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4">
-        <v>0</v>
-      </c>
-      <c r="C4" s="4">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>0</v>
-      </c>
-      <c r="E4" s="4">
-        <v>0</v>
-      </c>
-      <c r="F4" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="4">
-        <v>0</v>
-      </c>
-      <c r="C5" s="4">
-        <v>0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="3">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="4">
-        <v>0</v>
-      </c>
-      <c r="C6" s="4">
-        <v>0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>0</v>
-      </c>
-      <c r="E6" s="4">
-        <v>0</v>
-      </c>
-      <c r="F6" s="4">
+        <v>16</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
+    <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1659011e-6b88-4225-9a61-aaf33aaf19e8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{865EB4A8-5E98-485A-A3DB-A55C04192116}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B03187D-4177-424C-AE8C-216910DAB3B3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{75712F69-5552-4DED-B6F2-503AABF19EC9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>